--- a/Code and data/Initial data/Non sector data/DIVERS-RE_Potential.xlsx
+++ b/Code and data/Initial data/Non sector data/DIVERS-RE_Potential.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L227"/>
+  <dimension ref="A1:L231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -434,7 +434,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FR21</t>
+          <t>FRB0</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="K116">
-        <v>235.4409</v>
+        <v>398.094</v>
       </c>
     </row>
     <row r="117">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FR22</t>
+          <t>FRC1</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="K117">
-        <v>213.9675</v>
+        <v>266.3146</v>
       </c>
     </row>
     <row r="118">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FR23</t>
+          <t>FRC2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="K118">
-        <v>104.0782</v>
+        <v>70.23560000000001</v>
       </c>
     </row>
     <row r="119">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FR24</t>
+          <t>FRD1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="K119">
-        <v>398.094</v>
+        <v>183.8594</v>
       </c>
     </row>
     <row r="120">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FR25</t>
+          <t>FRD2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="K120">
-        <v>183.8594</v>
+        <v>104.0782</v>
       </c>
     </row>
     <row r="121">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FR26</t>
+          <t>FRE1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="K121">
-        <v>266.3146</v>
+        <v>124.2302</v>
       </c>
     </row>
     <row r="122">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FR30</t>
+          <t>FRE2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="K122">
-        <v>124.2302</v>
+        <v>213.9675</v>
       </c>
     </row>
     <row r="123">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FR41</t>
+          <t>FRF1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K123">
-        <v>118.2354</v>
+        <v>27.5727</v>
       </c>
     </row>
     <row r="124">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FR42</t>
+          <t>FRF2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="K124">
-        <v>27.5727</v>
+        <v>235.4409</v>
       </c>
     </row>
     <row r="125">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FR43</t>
+          <t>FRF3</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="K125">
-        <v>70.23560000000001</v>
+        <v>118.2354</v>
       </c>
     </row>
     <row r="126">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FR51</t>
+          <t>FRG0</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FR52</t>
+          <t>FRH0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FR53</t>
+          <t>FRI1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="K128">
-        <v>274.1792</v>
+        <v>218.0832</v>
       </c>
     </row>
     <row r="129">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FR61</t>
+          <t>FRI2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="K129">
-        <v>218.0832</v>
+        <v>116.8798</v>
       </c>
     </row>
     <row r="130">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FR62</t>
+          <t>FRI3</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="K130">
-        <v>360.3365</v>
+        <v>274.1792</v>
       </c>
     </row>
     <row r="131">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FR63</t>
+          <t>FRJ1</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="K131">
-        <v>116.8798</v>
+        <v>202.9781</v>
       </c>
     </row>
     <row r="132">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FR71</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="K132">
-        <v>201.2436</v>
+        <v>360.3365</v>
       </c>
     </row>
     <row r="133">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FR72</t>
+          <t>FRK1</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FR81</t>
+          <t>FRK2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="K134">
-        <v>202.9781</v>
+        <v>201.2436</v>
       </c>
     </row>
     <row r="135">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FR82</t>
+          <t>FRL0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FR83</t>
+          <t>FRM0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>HU10</t>
+          <t>HU21</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K139">
-        <v>37.2316</v>
+        <v>76.7715</v>
       </c>
     </row>
     <row r="140">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HU21</t>
+          <t>HU22</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="K140">
-        <v>76.7715</v>
+        <v>69.7184</v>
       </c>
     </row>
     <row r="141">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>HU22</t>
+          <t>HU23</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="K141">
-        <v>69.7184</v>
+        <v>98.51390000000001</v>
       </c>
     </row>
     <row r="142">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>HU23</t>
+          <t>HU31</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="K142">
-        <v>98.51390000000001</v>
+        <v>50.6581</v>
       </c>
     </row>
     <row r="143">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HU31</t>
+          <t>HU32</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="K143">
-        <v>50.6581</v>
+        <v>88.8775</v>
       </c>
     </row>
     <row r="144">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>HU32</t>
+          <t>HU33</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -5418,18 +5418,18 @@
         </is>
       </c>
       <c r="K144">
-        <v>88.8775</v>
+        <v>121.1625</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>HU33</t>
+          <t>ITC1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -5453,18 +5453,18 @@
         </is>
       </c>
       <c r="K145">
-        <v>121.1625</v>
+        <v>104.8681</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>IE01</t>
+          <t>ITC2</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -5488,18 +5488,18 @@
         </is>
       </c>
       <c r="K146">
-        <v>361.402</v>
+        <v>5.7051</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>IE02</t>
+          <t>ITC3</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="K147">
-        <v>407.8068</v>
+        <v>10.5356</v>
       </c>
     </row>
     <row r="148">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ITC1</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="K148">
-        <v>104.8681</v>
+        <v>116.1404</v>
       </c>
     </row>
     <row r="149">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ITC2</t>
+          <t>ITF1</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="K149">
-        <v>5.7051</v>
+        <v>36.6945</v>
       </c>
     </row>
     <row r="150">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ITC3</t>
+          <t>ITF2</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="K150">
-        <v>10.5356</v>
+        <v>26.7866</v>
       </c>
     </row>
     <row r="151">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="K151">
-        <v>116.1404</v>
+        <v>69.1247</v>
       </c>
     </row>
     <row r="152">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ITF1</t>
+          <t>ITF4</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="K152">
-        <v>36.6945</v>
+        <v>213.844</v>
       </c>
     </row>
     <row r="153">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ITF2</t>
+          <t>ITF5</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="K153">
-        <v>26.7866</v>
+        <v>68.9853</v>
       </c>
     </row>
     <row r="154">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>ITF6</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -5768,7 +5768,7 @@
         </is>
       </c>
       <c r="K154">
-        <v>69.1247</v>
+        <v>76.85429999999999</v>
       </c>
     </row>
     <row r="155">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ITF4</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="K155">
-        <v>213.844</v>
+        <v>229.9639</v>
       </c>
     </row>
     <row r="156">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ITF5</t>
+          <t>ITG2</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="K156">
-        <v>68.9853</v>
+        <v>175.5258</v>
       </c>
     </row>
     <row r="157">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ITF6</t>
+          <t>ITH1</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="K157">
-        <v>76.85429999999999</v>
+        <v>11.5094</v>
       </c>
     </row>
     <row r="158">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ITG1</t>
+          <t>ITH2</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="K158">
-        <v>229.9639</v>
+        <v>10.1845</v>
       </c>
     </row>
     <row r="159">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ITG2</t>
+          <t>ITH3</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="K159">
-        <v>175.5258</v>
+        <v>95.5318</v>
       </c>
     </row>
     <row r="160">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ITH1</t>
+          <t>ITH4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="K160">
-        <v>11.5094</v>
+        <v>28.7687</v>
       </c>
     </row>
     <row r="161">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ITH2</t>
+          <t>ITH5</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="K161">
-        <v>10.1845</v>
+        <v>119.2114</v>
       </c>
     </row>
     <row r="162">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>ITI1</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="K162">
-        <v>95.5318</v>
+        <v>84.2349</v>
       </c>
     </row>
     <row r="163">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ITH4</t>
+          <t>ITI2</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="K163">
-        <v>28.7687</v>
+        <v>39.2138</v>
       </c>
     </row>
     <row r="164">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ITH5</t>
+          <t>ITI3</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="K164">
-        <v>119.2114</v>
+        <v>52.7483</v>
       </c>
     </row>
     <row r="165">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ITI1</t>
+          <t>ITI4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -6153,18 +6153,18 @@
         </is>
       </c>
       <c r="K165">
-        <v>84.2349</v>
+        <v>83.334</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ITI2</t>
+          <t>LU00</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -6188,18 +6188,18 @@
         </is>
       </c>
       <c r="K166">
-        <v>39.2138</v>
+        <v>7.8957</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ITI3</t>
+          <t>LV00</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -6223,18 +6223,18 @@
         </is>
       </c>
       <c r="K167">
-        <v>52.7483</v>
+        <v>295.0738</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ITI4</t>
+          <t>MT00</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -6258,18 +6258,18 @@
         </is>
       </c>
       <c r="K168">
-        <v>83.334</v>
+        <v>2.6127</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>LT00</t>
+          <t>NL11</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -6293,18 +6293,18 @@
         </is>
       </c>
       <c r="K169">
-        <v>524.6721</v>
+        <v>27.6286</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>LU00</t>
+          <t>NL12</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -6328,18 +6328,18 @@
         </is>
       </c>
       <c r="K170">
-        <v>7.8957</v>
+        <v>23.5668</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>LV00</t>
+          <t>NL13</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -6363,18 +6363,18 @@
         </is>
       </c>
       <c r="K171">
-        <v>295.0738</v>
+        <v>25.7826</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MT00</t>
+          <t>NL21</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="K172">
-        <v>2.6127</v>
+        <v>29.9043</v>
       </c>
     </row>
     <row r="173">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NL11</t>
+          <t>NL22</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="K173">
-        <v>27.6286</v>
+        <v>32.9491</v>
       </c>
     </row>
     <row r="174">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NL12</t>
+          <t>NL23</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="K174">
-        <v>23.5668</v>
+        <v>15.6592</v>
       </c>
     </row>
     <row r="175">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NL13</t>
+          <t>NL31</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="K175">
-        <v>25.7826</v>
+        <v>11.0875</v>
       </c>
     </row>
     <row r="176">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NL21</t>
+          <t>NL32</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="K176">
-        <v>29.9043</v>
+        <v>25.089</v>
       </c>
     </row>
     <row r="177">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NL22</t>
+          <t>NL33</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="K177">
-        <v>32.9491</v>
+        <v>24.6246</v>
       </c>
     </row>
     <row r="178">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>NL34</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="K178">
-        <v>15.6592</v>
+        <v>17.039</v>
       </c>
     </row>
     <row r="179">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NL31</t>
+          <t>NL41</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="K179">
-        <v>11.0875</v>
+        <v>35.8731</v>
       </c>
     </row>
     <row r="180">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NL32</t>
+          <t>NL42</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -6678,18 +6678,18 @@
         </is>
       </c>
       <c r="K180">
-        <v>25.089</v>
+        <v>14.9161</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NL33</t>
+          <t>PL21</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -6713,18 +6713,18 @@
         </is>
       </c>
       <c r="K181">
-        <v>24.6246</v>
+        <v>47.2856</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NL34</t>
+          <t>PL22</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -6748,18 +6748,18 @@
         </is>
       </c>
       <c r="K182">
-        <v>17.039</v>
+        <v>37.7696</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NL41</t>
+          <t>PL41</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -6783,18 +6783,18 @@
         </is>
       </c>
       <c r="K183">
-        <v>35.8731</v>
+        <v>133.0752</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>NL42</t>
+          <t>PL42</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="K184">
-        <v>14.9161</v>
+        <v>89.3098</v>
       </c>
     </row>
     <row r="185">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>PL11</t>
+          <t>PL43</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="K185">
-        <v>79.6867</v>
+        <v>35.0847</v>
       </c>
     </row>
     <row r="186">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>PL12</t>
+          <t>PL51</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="K186">
-        <v>130.5836</v>
+        <v>82.5086</v>
       </c>
     </row>
     <row r="187">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>PL21</t>
+          <t>PL52</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="K187">
-        <v>47.2856</v>
+        <v>39.0319</v>
       </c>
     </row>
     <row r="188">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>PL61</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="K188">
-        <v>37.7696</v>
+        <v>82.3745</v>
       </c>
     </row>
     <row r="189">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PL31</t>
+          <t>PL62</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="K189">
-        <v>116.653</v>
+        <v>105.463</v>
       </c>
     </row>
     <row r="190">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>PL32</t>
+          <t>PL63</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="K190">
-        <v>54.0491</v>
+        <v>70.5252</v>
       </c>
     </row>
     <row r="191">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PL33</t>
+          <t>PL71</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="K191">
-        <v>38.6139</v>
+        <v>79.6867</v>
       </c>
     </row>
     <row r="192">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>PL34</t>
+          <t>PL72</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="K192">
-        <v>73.63939999999999</v>
+        <v>38.6139</v>
       </c>
     </row>
     <row r="193">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>PL41</t>
+          <t>PL81</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="K193">
-        <v>133.0752</v>
+        <v>116.653</v>
       </c>
     </row>
     <row r="194">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>PL42</t>
+          <t>PL82</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="K194">
-        <v>89.3098</v>
+        <v>54.0491</v>
       </c>
     </row>
     <row r="195">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>PL43</t>
+          <t>PL84</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -7203,18 +7203,18 @@
         </is>
       </c>
       <c r="K195">
-        <v>35.0847</v>
+        <v>73.63939999999999</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>PL51</t>
+          <t>PT11</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -7238,18 +7238,18 @@
         </is>
       </c>
       <c r="K196">
-        <v>82.5086</v>
+        <v>88.2971</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>PL52</t>
+          <t>PT15</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -7273,18 +7273,18 @@
         </is>
       </c>
       <c r="K197">
-        <v>39.0319</v>
+        <v>17.402</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>PL61</t>
+          <t>PT16</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -7308,18 +7308,18 @@
         </is>
       </c>
       <c r="K198">
-        <v>82.3745</v>
+        <v>79.3456</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PL62</t>
+          <t>PT17</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -7343,18 +7343,18 @@
         </is>
       </c>
       <c r="K199">
-        <v>105.463</v>
+        <v>17.5846</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PL63</t>
+          <t>PT18</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -7378,18 +7378,18 @@
         </is>
       </c>
       <c r="K200">
-        <v>70.5252</v>
+        <v>165.5418</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>PT11</t>
+          <t>RO11</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -7413,18 +7413,18 @@
         </is>
       </c>
       <c r="K201">
-        <v>88.2971</v>
+        <v>145.6246</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>PT15</t>
+          <t>RO12</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -7448,18 +7448,18 @@
         </is>
       </c>
       <c r="K202">
-        <v>17.402</v>
+        <v>131.8423</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>PT16</t>
+          <t>RO21</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -7483,18 +7483,18 @@
         </is>
       </c>
       <c r="K203">
-        <v>79.3456</v>
+        <v>227.9798</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PT17</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -7518,18 +7518,18 @@
         </is>
       </c>
       <c r="K204">
-        <v>17.5846</v>
+        <v>271.789</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PT18</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="K205">
-        <v>165.5418</v>
+        <v>237.843</v>
       </c>
     </row>
     <row r="206">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>RO11</t>
+          <t>RO32</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="K206">
-        <v>145.6246</v>
+        <v>15.001</v>
       </c>
     </row>
     <row r="207">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>RO12</t>
+          <t>RO41</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -7623,7 +7623,7 @@
         </is>
       </c>
       <c r="K207">
-        <v>131.8423</v>
+        <v>154.6314</v>
       </c>
     </row>
     <row r="208">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>RO21</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -7658,18 +7658,18 @@
         </is>
       </c>
       <c r="K208">
-        <v>227.9798</v>
+        <v>147.042</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>SE11</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -7693,18 +7693,18 @@
         </is>
       </c>
       <c r="K209">
-        <v>271.789</v>
+        <v>10.1791</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>SE12</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -7728,18 +7728,18 @@
         </is>
       </c>
       <c r="K210">
-        <v>237.843</v>
+        <v>60.2681</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>RO32</t>
+          <t>SE21</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -7763,18 +7763,18 @@
         </is>
       </c>
       <c r="K211">
-        <v>15.001</v>
+        <v>43.933</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>RO41</t>
+          <t>SE22</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -7798,18 +7798,18 @@
         </is>
       </c>
       <c r="K212">
-        <v>154.6314</v>
+        <v>44.2639</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>SE23</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="K213">
-        <v>147.042</v>
+        <v>67.08880000000001</v>
       </c>
     </row>
     <row r="214">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>SE31</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -7868,7 +7868,7 @@
         </is>
       </c>
       <c r="K214">
-        <v>10.1791</v>
+        <v>33.2285</v>
       </c>
     </row>
     <row r="215">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SE12</t>
+          <t>SE32</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="K215">
-        <v>60.2681</v>
+        <v>99.8385</v>
       </c>
     </row>
     <row r="216">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>SE21</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -7938,18 +7938,18 @@
         </is>
       </c>
       <c r="K216">
-        <v>43.933</v>
+        <v>180.5373</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>SE22</t>
+          <t>SI03</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -7973,18 +7973,18 @@
         </is>
       </c>
       <c r="K217">
-        <v>44.2639</v>
+        <v>34.0627</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SE23</t>
+          <t>SI04</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -8008,18 +8008,18 @@
         </is>
       </c>
       <c r="K218">
-        <v>67.08880000000001</v>
+        <v>14.3152</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SE31</t>
+          <t>SK01</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -8043,18 +8043,18 @@
         </is>
       </c>
       <c r="K219">
-        <v>33.2285</v>
+        <v>11.2176</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>SK02</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -8078,18 +8078,18 @@
         </is>
       </c>
       <c r="K220">
-        <v>99.8385</v>
+        <v>115.7805</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>SK03</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -8113,18 +8113,18 @@
         </is>
       </c>
       <c r="K221">
-        <v>180.5373</v>
+        <v>35.0366</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>SI03</t>
+          <t>SK04</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -8148,18 +8148,18 @@
         </is>
       </c>
       <c r="K222">
-        <v>34.0627</v>
+        <v>37.8183</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>SI04</t>
+          <t>PL91</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -8183,18 +8183,18 @@
         </is>
       </c>
       <c r="K223">
-        <v>14.3152</v>
+        <v>22.5612</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>SK01</t>
+          <t>PL92</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -8218,18 +8218,18 @@
         </is>
       </c>
       <c r="K224">
-        <v>11.2176</v>
+        <v>108.0224</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>SK02</t>
+          <t>HU11</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -8253,18 +8253,18 @@
         </is>
       </c>
       <c r="K225">
-        <v>115.7805</v>
+        <v>2.8225</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>SK03</t>
+          <t>HU12</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -8288,18 +8288,18 @@
         </is>
       </c>
       <c r="K226">
-        <v>35.0366</v>
+        <v>34.4091</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SK04</t>
+          <t>LT01</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -8323,7 +8323,147 @@
         </is>
       </c>
       <c r="K227">
-        <v>37.8183</v>
+        <v>78.6986</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>LT02</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>RE_Potential</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>TWh (technical potential, medium scenario)</t>
+        </is>
+      </c>
+      <c r="K228">
+        <v>445.9735</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>IE05</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>RE_Potential</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>TWh (technical potential, medium scenario)</t>
+        </is>
+      </c>
+      <c r="K229">
+        <v>325.2</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>IE06</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>RE_Potential</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>TWh (technical potential, medium scenario)</t>
+        </is>
+      </c>
+      <c r="K230">
+        <v>159.6761</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>IE04</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>RE_Potential</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>TWh (technical potential, medium scenario)</t>
+        </is>
+      </c>
+      <c r="K231">
+        <v>284.3329</v>
       </c>
     </row>
   </sheetData>
